--- a/www/download/COUNTRY.NLD.EXI382.xlsx
+++ b/www/download/COUNTRY.NLD.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Países Baixos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2556</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>8.724</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>6.811</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>7.04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>7.35</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>7.496</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7.651</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>7.926</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>7.701</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>8.03</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>8.049</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>8.233</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>8.462</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>8.104</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>7.902</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>7.567</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>7.579</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>7.322</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>7.382</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7.229</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>7.218</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7.493</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>7.55</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>7.619</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>7.635</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>7.378</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.015</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>6.001</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>6.203</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6.54</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6.68</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6.829</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>7.04</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>6.842</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>7.272</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>7.121</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>7.102</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>7.235</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>7.365</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>7.081</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>6.904</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>6.517</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>6.453</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>6.505</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>6.264</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>6.293</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6.137</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>6.105</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6.331</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>6.356</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>6.381</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>6.392</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>14852.575</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>11133.426</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>11959.601</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>12299.631</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>12760.614</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>12934.605</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12868.342</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>13374.452</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>12545.298</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>13312.965</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>12999.435</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>13483.77</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>13913.697</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>14286.945</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>13548.049</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>13081.378</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>12511.437</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>12410.031</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>12543.872</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>12127.138</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>12235.599</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>12059.68</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>11970.243</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12360.951</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>12505.993</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12680.728</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>12691.308</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12202.995</t>
+          <t>31959228422.6614</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7425.578</t>
+          <t>29640661621.2697</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8156.605</t>
+          <t>27522466183.2844</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8431.127</t>
+          <t>27931093192.8534</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8924.724</t>
+          <t>31414888326.048</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9068.079</t>
+          <t>31452677565.8593</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9248.854</t>
+          <t>33052550819.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9516.986</t>
+          <t>32115153965.4911</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8876.196</t>
+          <t>30014952573.1964</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9616.107</t>
+          <t>33061623860.7299</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9147.307</t>
+          <t>31422585862.4681</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9476.798</t>
+          <t>32706858221.9715</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9639.301</t>
+          <t>29470142459.8828</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>9602.604</t>
+          <t>34420777815.1975</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9239.825</t>
+          <t>31332700209.7526</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>8978.902</t>
+          <t>31994560080.9543</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>8182.999</t>
+          <t>29230667349.8845</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>8198.201</t>
+          <t>34143595753.9709</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>8140.528</t>
+          <t>36607601554.8589</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>9961.397</t>
+          <t>28828685390.3857</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>10020.925</t>
+          <t>26352658947.4947</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>9846.405</t>
+          <t>30625959825.3725</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>9723.526</t>
+          <t>26669829688.8433</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10022.39</t>
+          <t>30003539516.8878</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>10118.114</t>
+          <t>28852108128.7036</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10221.229</t>
+          <t>32499312598.1863</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>10243.9</t>
+          <t>36153151892.9953</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13741468298.1349</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>16587405340.64</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>14289840010.8403</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>16016239648.524</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>17736600355.4858</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>18912978370.6802</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19047967832.0076</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>20379466220.2697</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>19381406228.6061</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>19308998965.2146</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>18213092714.938</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>19177176051.2055</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>14983891133.5133</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>17369660036.6993</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>20316289761.5645</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>20075343949.9406</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>15302068286.0414</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>18107459450.2409</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>17705827858.7522</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>18883796437.9389</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>19951659428.3827</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>19904352366.5566</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>20946732293.1328</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22083294790.741</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22644396656.5016</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>26646241215.4235</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>27500661250.3238</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>558988202.207007</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9993498.49409731</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8350176573.11934</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6680691.51777019</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7589736.13606082</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>12546904318.5381</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>334207392249.956</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5862404.63706147</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5427347.86741066</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5852247.55409869</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>14849050510.5017</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5250402.15540615</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4729474.73709109</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5314502.46251183</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4916802.15195212</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>433190021.088604</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4176951.10800345</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4592260.04996403</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4830592.54871623</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>190050306.46853</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>190487112.770428</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>190091458.65707</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>11047970.1517367</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11032709.0982941</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>10843528.3557134</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11104388.9370067</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>11164678.9587901</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>31791.7182951521</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>44989.0007306907</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>52394.2641935213</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>55446.0273306084</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>60506.5676519605</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>72586.7651151462</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>71355.5547774886</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>71764.6310522946</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>61405.6065960999</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>64132.2648154363</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>68182.4028131933</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>76322.1428721186</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>81426.8696496321</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>83325.4703586432</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>80987.1065124287</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>90508.9329727647</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>90850.1401184701</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>98759.023026215</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>96923.0422204836</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>95108.6307940981</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>108478.180821175</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>98891.9493511959</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>102737.329805891</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>101312.204321661</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>111090.518812533</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>108535.490698564</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>107992.729168959</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>119131.304289781</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>225241.534522107</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>227793.104670567</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>237664.024626717</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>281957.885296066</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>337449.910720499</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>356066.915821084</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>335366.885736515</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>287926.883306015</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>309933.607082702</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>315789.816548241</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>351608.86178732</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>328235.857745767</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>385220.462903223</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>351400.904625271</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>413797.15512123</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>393570.789191942</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>507419.896563101</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>531431.792121376</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>433186.7120604</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>447313.910476114</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>473827.631598019</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>436240.821812058</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>477309.949127087</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>489039.503253122</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>524033.769145962</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>572328.261373401</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.111958452990471</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.552336375249227</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.429202496752046</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.473588858245044</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.4968187915876</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.52053670118634</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.514444056102492</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.533011027024259</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.542025181490755</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.501988320713915</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.4977620142185</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.505829326763565</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.356689066003568</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.447162236928524</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.54520116081995</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.552739817440288</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.46523575460313</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.547247308628396</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.540234545092167</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.472489710968026</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.49773979073256</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.50531398838315</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.535797487105395</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.546155141055574</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.553173629254867</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.616410109342729</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.627503505077249</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1862.46981026461</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2757.85677196162</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2381.08441544383</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2581.89022754368</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2712.05987178467</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2831.36895875356</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2789.19461020446</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2894.89278392359</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2832.66924315639</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2655.25288300539</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2557.69533555284</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2700.36414537356</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2070.97124246913</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2358.53407336362</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2869.28929209089</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2907.78446551885</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2347.84323529645</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2806.0963985563</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2721.7960798666</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>3014.82399100717</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>3170.69859026946</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3243.54989971706</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>3431.06347683415</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>3488.06456774164</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>3562.66965450586</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>4175.86951565703</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4302.09986595999</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>33239587250.7839</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>24606628728.6664</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>22190436932.7044</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>22946070833.851</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>25772673510.2488</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>26958110985.8122</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>28884252703.7062</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>30782521375.8725</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>30109047256.5468</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>33854208967.4951</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>32636792379.1488</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>31762205415.5494</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>24453453024.9337</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>30066617110.6474</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>29806177991.9302</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>29366379211.9599</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>26019597117.1881</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>28488198291.9421</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>30352112343.5418</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>27992501863.6301</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>26575485571.4132</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>30950823392.2038</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>30224330597.2819</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>32721394466.8412</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>31742861102.917</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>34957575848.8545</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>36373740407.6336</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16807381133.8956</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20530162126.6213</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17766836243.6558</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>17687355186.0742</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20566115025.135</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>21622549924.7175</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23593408861.8438</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>24822955232.3814</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>23307335494.8214</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>25457410575.2572</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>24817118926.4279</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>24676885252.7251</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>18769183170.098</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>24109961464.651</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>23363347738.0021</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>23358480534.9888</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>19966095805.9588</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>22025128917.6485</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>24059668920.1892</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>21468982659.3085</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>19117906401.1572</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>22460069434.0556</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>22708640203.4358</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>24965018538.3901</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>23897586951.9027</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>26201735904.0408</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>26387285049.7048</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16432206116.8882</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4076466602.04509</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4423600689.04866</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>5258715647.77687</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5206558485.11379</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5335561061.0947</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5290843841.86241</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5959566143.49106</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6801711761.72547</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>8396798392.23792</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>7819673452.72094</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7085320162.82428</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>5684269854.83566</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>5956655645.99646</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6442830253.92805</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>6007898676.97117</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>6053501311.2293</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>6463069374.29364</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>6292443423.35255</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>6523519204.32158</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>7457579170.25605</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>8490753958.14821</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>7515690393.84603</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>7756375928.45113</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>7845274151.0143</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>8755839944.81373</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>9986455357.92878</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>1653.95057156593</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>1234.5921590798</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>1359.11703935795</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>1359.13578256723</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>1364.65756357139</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>1357.53750112258</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>1354.31002167167</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>1351.88300803936</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>1297.29118253127</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1322.34694719473</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1284.57175357079</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1334.44076770278</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>1332.27844427257</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>1303.8867012462</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1304.94943931469</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.144</t>
+          <t>1300.53621089225</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1255.54261603345</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1270.46769669453</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1251.38781282623</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1590.35067487672</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1592.51573747272</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1604.53876337127</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1592.70828784731</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1583.04017173576</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1591.89475188667</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1601.82133090991</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1602.51712087774</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1702.50965879979</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>1625.2702110889</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1755.92438702154</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1747.18112987741</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1736.1615804298</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1725.44221226174</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>1681.80644318118</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>1687.45766988757</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>1629.04791585464</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1633.43251168681</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1618.87881542759</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>1675.29383992186</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>1690.0937746736</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1688.28523822981</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>1671.73181807134</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>1655.53533461581</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>1653.33364167347</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>1661.31606425702</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>1655.14824442125</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>1656.27107399033</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>1657.55406001845</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1668.25789908424</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>1658.49337772971</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1649.6755641757</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>1656.46008660685</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>1664.33387366832</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>1662.31341988811</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>159120.65630319</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>193411.34806904</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>205047.517313082</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>214061.680750115</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>232326.978699926</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>282155.203263632</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>293402.250783131</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>287846.358844395</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>269957.225970084</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>268637.874059807</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>279075.370798733</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>277632.157643561</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>280197.886560081</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>273949.183120726</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>279310.186062286</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>292589.773005599</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>304292.343156344</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>339046.172739107</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>346825.008493188</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>366894.693147574</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>454517.297789459</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>450785.984541012</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>485226.135131626</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>507774.916869775</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>533590.187167806</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>561709.189071237</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>593326.126643483</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7159683653.89687</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10994609279.2756</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10303265772.7406</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10572756163.3365</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>11697794252.1117</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>12504638797.5004</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12659011480.853</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11601479266.6767</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>10230650994.5149</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10587901761.5085</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10190923397.1519</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>9986190390.59576</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>8365346492.11073</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>9986167695.0683</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>9847020642.90858</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>10331497307.1994</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>9030399097.23707</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>11464130683.6959</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>13015160238.4871</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>10320093060.9029</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>10773271726.5894</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>12158210169.8739</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>11662021386.4054</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13362755343.4324</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>12661141432.0727</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15072517749.1845</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>15986130688.661</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>129164.176634174</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>165363.56701637</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>174380.246026994</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>182741.705459897</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>202666.535316515</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>243557.52351198</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>252101.608383795</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>243226.55215154</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>225465.106572445</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>215150.277197629</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>218159.056192601</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>212011.957985894</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>222829.940873055</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>202055.152441134</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>217572.026711746</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>225057.373071163</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>231790.44565916</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>255869.044551036</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>258632.131318431</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>269503.792177278</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>386842.960831998</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>356238.380374089</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>381385.745735226</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>401037.07254743</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>423064.088022608</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>453054.132038384</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>484881.560373416</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14852.575</t>
+          <t>23428139123.1917</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11133.426</t>
+          <t>29903666491.2587</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11959.601</t>
+          <t>26753166201.0593</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12299.631</t>
+          <t>27618196253.5789</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12760.614</t>
+          <t>32029440564.2645</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12934.605</t>
+          <t>33474683422.4777</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12868.342</t>
+          <t>34882338351.5929</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13374.452</t>
+          <t>34917609954.9416</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12545.298</t>
+          <t>32781481248.6666</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>13312.965</t>
+          <t>34633028810.2269</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>12999.435</t>
+          <t>32639426564.0042</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>13483.77</t>
+          <t>31984654771.3768</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>13913.697</t>
+          <t>25694710108.0525</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>14286.945</t>
+          <t>30200473612.2506</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>13548.049</t>
+          <t>30565871910.1939</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>13081.378</t>
+          <t>31370995435.942</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>12511.437</t>
+          <t>26689385143.3482</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12410.031</t>
+          <t>30883424252.9202</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>12543.872</t>
+          <t>33264464816.5232</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>12127.138</t>
+          <t>27959348793.2792</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>12235.599</t>
+          <t>30807025406.6872</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>12059.68</t>
+          <t>33081642579.7115</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>11970.243</t>
+          <t>31884159386.6777</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12360.951</t>
+          <t>35475506827.4682</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>12505.993</t>
+          <t>34316572159.9242</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12680.728</t>
+          <t>39486062740.5518</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>12691.308</t>
+          <t>41793566758.3993</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12202.995</t>
+          <t>29956.4796690161</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7425.578</t>
+          <t>28047.7810526704</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8156.605</t>
+          <t>30667.2712860878</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8431.127</t>
+          <t>31319.9752902176</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8924.724</t>
+          <t>29660.4433834111</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9068.079</t>
+          <t>38597.6797516517</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9248.854</t>
+          <t>41300.6423993353</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9516.986</t>
+          <t>44619.8066928557</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8876.196</t>
+          <t>44492.1193976389</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9616.107</t>
+          <t>53487.5968621779</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9147.307</t>
+          <t>60916.3146061316</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9476.798</t>
+          <t>65620.1996576669</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>9639.301</t>
+          <t>57367.9456870265</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>9602.604</t>
+          <t>71894.0306795921</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9239.825</t>
+          <t>61738.1593505399</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>8978.902</t>
+          <t>67532.3999344362</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>8182.999</t>
+          <t>72501.8974971837</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>8198.201</t>
+          <t>83177.1281880709</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>8140.528</t>
+          <t>88192.8771747574</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>9961.397</t>
+          <t>97390.9009702962</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>10020.925</t>
+          <t>67674.3369574615</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>9846.405</t>
+          <t>94547.6041669225</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>9723.526</t>
+          <t>103840.389396399</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10022.39</t>
+          <t>106737.844322345</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>10118.114</t>
+          <t>110526.099145198</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10221.229</t>
+          <t>108655.057032853</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>10243.9</t>
+          <t>108444.566270067</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26712.774</t>
+          <t>-16268455469.2949</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24758.279</t>
+          <t>-18909057211.9831</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23010.684</t>
+          <t>-16449900428.3187</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23294.301</t>
+          <t>-17045440090.2424</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>25915.528</t>
+          <t>-20331646312.1528</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26036.773</t>
+          <t>-20970044624.9773</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27154.43</t>
+          <t>-22223326870.74</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26467.357</t>
+          <t>-23316130688.265</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24908.617</t>
+          <t>-22550830254.1517</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27203.643</t>
+          <t>-24045127048.7183</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>25863.992</t>
+          <t>-22448503166.8523</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>26882.421</t>
+          <t>-21998464380.7811</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>24605.94</t>
+          <t>-17329363615.9417</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>28290.092</t>
+          <t>-20214305917.1823</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>26051.037</t>
+          <t>-20718851267.2853</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>26452.143</t>
+          <t>-21039498128.7426</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>23993.639</t>
+          <t>-17658986046.1111</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>27853.314</t>
+          <t>-19419293569.2244</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>29801.245</t>
+          <t>-20249304578.0361</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>23533.362</t>
+          <t>-17639255732.3763</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>21760.607</t>
+          <t>-20033753680.0978</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>24911.13</t>
+          <t>-20923432409.8376</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>22112.491</t>
+          <t>-20222138000.2722</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>24622.497</t>
+          <t>-22112751484.0358</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>23830.21</t>
+          <t>-21655430727.8515</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>26672.187</t>
+          <t>-24413544991.3673</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>29187.878</t>
+          <t>-25807436069.7383</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>128438.075795237</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>130711.869335344</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>131762.560857098</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>147389.372227686</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>149346.57465424</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>158569.618863184</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>181676.925362737</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>189974.28585543</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>191477.671637707</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>198589.94025328</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>200760.323529312</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>211228.945116638</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>213452.906002194</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>225823.747818159</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>223283.506081512</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>223675.85904518</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>226047.51214553</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>222195.704471267</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>215847.998780645</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>221604.692395095</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>224949.948103047</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>231225.37039151</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>247200.355267333</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>244812.551558767</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>268706.025549356</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>276264.183364046</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>286350.007920227</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>8528.73</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5920.328</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>6330.391</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>6516.208</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>6741.457</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>6765.591</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6623.707</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>6872.271</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>6401.231</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>6841.197</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>6784.473</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>7099.53</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>7310.784</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>7445.418</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>7221.224</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>6998.099</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>6747.478</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>6645.361</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>6676.53</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>6329.503</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>6390.788</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>6391.904</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>6280.905</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>6368.45</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>6554.063</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>6731.11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6821.745</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>225947.494968802</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>230591.107212425</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>236457.007850728</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>275507.87110552</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>273844.70345569</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>301021.585879451</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>324632.342938535</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>341988.581821769</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>345305.139523169</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>358429.893708417</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>364616.027945753</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>383170.185214685</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>397938.210654842</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>422512.149110717</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>433377.139651349</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>428214.592352239</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>430731.3481027</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>432723.892331872</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>431812.486114059</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>460902.378360214</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>457647.760382438</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>466393.783307416</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>494699.299941569</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>509740.91255379</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>541695.706301758</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>556075.568997795</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>591082.97511917</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>11368.223</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>14441.023</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>12464.484</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>13955.839</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>15330.975</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>16350.819</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>16500.791</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>17750.707</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>17046.35</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>16867.207</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>15918.271</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>16564.709</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>13046.946</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>14927.677</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>17682.971</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>17292.353</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>13042.42</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>15485.201</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>15148.756</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>16301.405</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>17241.172</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>17280.002</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>18201.712</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>19156.412</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>19701.237</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>23122.908</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>23851.196</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7.34</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-48.58</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-34.56</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-39.59</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-41.79</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-44.54</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-43.95</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-46.39</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-47.93</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-42.99</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-42.54</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-42.79</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-26.12</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-35.67</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-47.75</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-48.08</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-37.26</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-47.06</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-46.26</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-38.89</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-41.88</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-43.02</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-46.58</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-47.68</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-48.64</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-55.8</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-57.05</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>700.425</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>11.342</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>10483.391</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>7.253</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8.205</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>15752.8</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>419629.711</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>6.228</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>5.789</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6.222</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>18643.418</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>5.598</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>5.155</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>5.646</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>543.011</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>4.432</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>4.827</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>5.093</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>237.82</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>238.539</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>237.944</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>13.244</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13.183</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>12.985</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13.279</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>13.276</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>190998.896789061</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>195709.264006584</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>203333.686066466</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>189259.315140795</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>227246.652608063</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>236262.283913032</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>249611.559044642</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>253120.967647848</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>266332.699094387</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>271019.226682676</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>290943.621459891</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>311543.497564056</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>335678.043120518</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>341516.190961458</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>305822.264094249</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>334000.991403912</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>341321.07821219</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>343524.85178938</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>356077.576025741</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>329255.14489583</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>363853.039649626</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>375807.894785285</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>384585.627781155</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>411275.47146781</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>423367.065902835</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>426577.081797833</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>399412.777468482</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12202994765.6581</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7425578000.00124</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>8156605000.00035</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8431127000.00051</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8924724000.00115</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9068078999.99772</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9248853999.99984</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9516985999.99758</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8876195999.99981</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9616106999.9998</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9147307000.00216</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>9476797999.99786</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>9639301000.00131</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>9602604000.00086</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9239825000.00509</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>8978901999.99942</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>8182998999.99629</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>8198200999.99876</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>8140527999.99898</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>9961396916.99811</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>10020924639.7322</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>9846404686.02831</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>9723525767.40281</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10022389809.332</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>10118113575.7378</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10221228754.2516</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>10243899923.8036</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>14852575410.2174</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>11133426000.001</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11959601000.0005</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>12299630999.9997</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>12760614000.0018</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>12934604999.9978</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12868342000.0003</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13374451999.9977</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>12545297999.9998</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>13312965000.0003</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>12999435000.0018</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>13483769999.999</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>13913697000.0014</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>14286945000.0002</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>13548049000.0053</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>13081377999.9999</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>12511436999.9978</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>12410030999.9974</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>12543871999.9982</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>12127137730.2632</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>12235598878.1007</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>12059679840.5622</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>11970242553.8239</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12360950698.5746</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>12505992816.4665</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12680727738.8102</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>12691307988.6382</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8528730487.76671</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5920327927.8253</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6330390757.65572</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6516207738.95884</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6741457376.80964</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6765591117.92579</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6623707499.09298</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>6872271155.98958</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6401230578.22085</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6841196850.58517</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6784472755.09172</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>7099529555.16053</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7310783974.4176</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>7445418345.50005</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7221224236.50341</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>6998099087.97418</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>6747477956.75017</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>6645360542.82386</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>6676529638.78733</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>6329503465.21963</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>6390788293.13033</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>6391904283.1422</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>6280904838.81881</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>6368450377.92959</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>6554062891.71286</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>6731109802.25339</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6821745149.56762</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8723930.18944044</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>6850199.99999987</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>6810999.99999821</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>7039700.00000098</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>7349900.00000046</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>7496399.99999935</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7651499.9999997</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7925800.00000165</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>7701000.00000196</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>8150299.99999959</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>8029899.99999987</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>8048600.0000023</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>8232500.0000006</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>8462400.00000257</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>8104199.99999494</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>7901599.99999976</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>7567399.99999878</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>7469999.99999849</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>7578700.00000176</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>7321952.25812053</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>7381719.34975351</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>7228906.18242069</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>7217540.15696454</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>7492958.59562004</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>7549830.45929237</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>7619100.91444626</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>7634726.30178993</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>7378089.1493659</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6014599.99999988</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6001399.99999819</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6203300.00000089</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6539900.00000046</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6679799.99999935</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6829199.99999975</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7039800.00000154</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6842100.00000202</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7271999.99999976</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7120899.99999992</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7101700.00000224</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7235200.00000033</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7364600.00000236</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7080599.99999504</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>6903999.99999946</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>6517499.99999863</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>6452899.99999892</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>6505200.00000144</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>6263648.05848262</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>6292512.15792387</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>6136595.08315038</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>6105026.16304272</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>6331102.63926075</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>6356019.18012867</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>6381004.27121009</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>6392380.95515182</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>14852575410.2174</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>11133426000.001</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>11959601000.0005</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>12299630999.9997</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>12760614000.0018</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>12934604999.9978</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12868342000.0003</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>13374451999.9977</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>12545297999.9998</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>13312965000.0003</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>12999435000.0018</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>13483769999.999</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>13913697000.0014</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>14286945000.0002</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>13548049000.0053</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>13081377999.9999</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>12511436999.9978</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>12410030999.9974</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>12543871999.9982</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>12127137730.2632</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>12235598878.1007</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>12059679840.5622</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>11970242553.8239</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12360950698.5746</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>12505992816.4665</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12680727738.8102</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>12691307988.6382</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>12202994765.6581</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>7425578000.00124</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8156605000.00035</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8431127000.00051</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8924724000.00115</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9068078999.99772</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9248853999.99984</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>9516985999.99758</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>8876195999.99981</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>9616106999.9998</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>9147307000.00216</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>9476797999.99786</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>9639301000.00131</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>9602604000.00086</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>9239825000.00509</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8978901999.99942</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8182998999.99629</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>8198200999.99876</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>8140527999.99898</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>9961396916.99811</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>10020924639.7322</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>9846404686.02831</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>9723525767.40281</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10022389809.332</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>10118113575.7378</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10221228754.2516</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>10243899923.8036</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>749947.611761595</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>785684.466330377</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>804358.825746743</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>857787.526922394</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>920184.961144476</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1017994.00564085</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1115261.28866616</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1132398.75002899</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1144909.98197689</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1189886.0187205</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1241101.2444414</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1312563.07923827</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1376753.54954657</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1429830.80800834</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1403084.70368719</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1436444.46962333</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1484622.55069828</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1534623.14846375</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1539180.59693338</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1570167.04489561</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1620795.75100398</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1657967.11915063</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1745112.99805513</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1817985.64728884</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1881434.68010544</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1923517.18188441</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1996223.26574027</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>243168.946989831</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>249762.760330434</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>258149.463959375</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>301308.948274966</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>299221.29777587</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>329875.828619877</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>354929.227812545</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>373132.661249129</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>376085.635058162</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>392362.484229273</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>400464.574566221</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>421759.797859433</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>440712.45976561</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>467805.23316145</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>475574.447638159</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>467790.006616282</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>474174.868258794</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>476378.925497253</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>472975.33434893</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>512834.53082035</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>502182.716046909</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>512978.793215515</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>542215.046824699</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>560505.172883248</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>593955.90307005</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>607419.810636322</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>650362.907544438</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
